--- a/outputs/reports/AZZAM_AUDIENCE_SEGMENTS.xlsx
+++ b/outputs/reports/AZZAM_AUDIENCE_SEGMENTS.xlsx
@@ -552,7 +552,7 @@
         <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
@@ -561,10 +561,10 @@
         <v>578</v>
       </c>
       <c r="M2" t="n">
-        <v>7657</v>
+        <v>9308</v>
       </c>
       <c r="N2" t="n">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="3">
@@ -600,7 +600,7 @@
         <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>1201</v>
+        <v>1213</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -609,7 +609,7 @@
         <v>1041</v>
       </c>
       <c r="M3" t="n">
-        <v>19104</v>
+        <v>20515</v>
       </c>
       <c r="N3" t="n">
         <v>58.7</v>
@@ -696,7 +696,7 @@
         <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -705,10 +705,10 @@
         <v>339</v>
       </c>
       <c r="M5" t="n">
-        <v>2424</v>
+        <v>3181</v>
       </c>
       <c r="N5" t="n">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
@@ -744,7 +744,7 @@
         <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -753,7 +753,7 @@
         <v>99</v>
       </c>
       <c r="M6" t="n">
-        <v>2354</v>
+        <v>2367</v>
       </c>
       <c r="N6" t="n">
         <v>6.4</v>
@@ -840,7 +840,7 @@
         <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -849,10 +849,10 @@
         <v>138</v>
       </c>
       <c r="M8" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
